--- a/data/trans_dic/P1801_2016_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1801_2016_2023-Estudios-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>60,77%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53,99; 60,96</t>
+          <t>54,17; 61,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>54,7; 62,98</t>
+          <t>51,68; 59,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62,36; 68,84</t>
+          <t>62,77; 68,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61,42; 67,04</t>
+          <t>61,77; 66,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>59,7; 64,4</t>
+          <t>59,61; 64,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,88; 64,46</t>
+          <t>58,64; 63,28</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>47,64%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>41,37; 45,57</t>
+          <t>41,26; 45,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44,05; 64,39</t>
+          <t>41,74; 46,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51,5; 56,01</t>
+          <t>51,69; 56,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47,08; 65,55</t>
+          <t>49,21; 53,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>47,08; 50,22</t>
+          <t>47,01; 50,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,1; 62,1</t>
+          <t>45,99; 49,05</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>56,97%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,68; 46,36</t>
+          <t>37,83; 46,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50,72; 59,83</t>
+          <t>49,63; 57,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49,73; 58,54</t>
+          <t>49,67; 58,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56,38; 63,26</t>
+          <t>56,86; 63,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>44,85; 51,19</t>
+          <t>44,66; 51,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>54,72; 60,3</t>
+          <t>54,12; 59,76</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>52,04%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>44,55; 47,95</t>
+          <t>44,6; 48,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,7; 64,14</t>
+          <t>46,29; 50,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55,49; 59,0</t>
+          <t>55,5; 58,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53,18; 65,28</t>
+          <t>54,34; 57,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,69; 53,09</t>
+          <t>50,74; 53,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,58; 60,92</t>
+          <t>50,94; 53,24</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>303393</t>
+          <t>322861</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>484577</t>
+          <t>526907</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>787970</t>
+          <t>849767</t>
         </is>
       </c>
     </row>
@@ -1101,32 +1101,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>407254; 459859</t>
+          <t>408665; 461890</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>281144; 323704</t>
+          <t>298440; 346386</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>620310; 684767</t>
+          <t>624345; 684699</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>463373; 505754</t>
+          <t>507076; 549005</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1044132; 1126294</t>
+          <t>1042617; 1127780</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>759484; 817582</t>
+          <t>820059; 884847</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1163660</t>
+          <t>984435</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1201306</t>
+          <t>1109857</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2364966</t>
+          <t>2094292</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1219,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>859091; 946238</t>
+          <t>856725; 952943</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1007851; 1473224</t>
+          <t>930030; 1039968</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1024032; 1113701</t>
+          <t>1027815; 1118903</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1052424; 1465283</t>
+          <t>1066473; 1150128</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1913676; 2041236</t>
+          <t>1910625; 2038786</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2130326; 2809090</t>
+          <t>2021573; 2155903</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>357015</t>
+          <t>380451</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>395007</t>
+          <t>442280</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>752022</t>
+          <t>822731</t>
         </is>
       </c>
     </row>
@@ -1337,32 +1337,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>206044; 253563</t>
+          <t>206898; 253311</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>327962; 386850</t>
+          <t>353151; 409925</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>273108; 321450</t>
+          <t>272758; 320143</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>371117; 416426</t>
+          <t>416563; 466339</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>491555; 561074</t>
+          <t>489449; 560156</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>714050; 786883</t>
+          <t>781673; 863083</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1824068</t>
+          <t>1687746</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2080889</t>
+          <t>2079043</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3904958</t>
+          <t>3766790</t>
         </is>
       </c>
     </row>
@@ -1455,32 +1455,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1504686; 1619619</t>
+          <t>1506277; 1625765</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1679422; 2211757</t>
+          <t>1628035; 1759284</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1960129; 2084021</t>
+          <t>1960156; 2079120</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1940116; 2381337</t>
+          <t>2021992; 2131967</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3502469; 3668338</t>
+          <t>3506054; 3670646</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3660270; 4323540</t>
+          <t>3687153; 3853892</t>
         </is>
       </c>
     </row>
